--- a/qa-correction-erreurs/ig/StructureDefinition-PersonneStructureAuteur.xlsx
+++ b/qa-correction-erreurs/ig/StructureDefinition-PersonneStructureAuteur.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-22T11:16:18+00:00</t>
+    <t>2025-08-22T11:39:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/qa-correction-erreurs/ig/StructureDefinition-PersonneStructureAuteur.xlsx
+++ b/qa-correction-erreurs/ig/StructureDefinition-PersonneStructureAuteur.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-22T11:39:32+00:00</t>
+    <t>2025-08-22T13:00:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/qa-correction-erreurs/ig/StructureDefinition-PersonneStructureAuteur.xlsx
+++ b/qa-correction-erreurs/ig/StructureDefinition-PersonneStructureAuteur.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-22T13:00:58+00:00</t>
+    <t>2025-08-22T15:38:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/qa-correction-erreurs/ig/StructureDefinition-PersonneStructureAuteur.xlsx
+++ b/qa-correction-erreurs/ig/StructureDefinition-PersonneStructureAuteur.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-22T15:38:31+00:00</t>
+    <t>2025-08-22T16:16:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/qa-correction-erreurs/ig/StructureDefinition-PersonneStructureAuteur.xlsx
+++ b/qa-correction-erreurs/ig/StructureDefinition-PersonneStructureAuteur.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-22T16:16:41+00:00</t>
+    <t>2025-08-25T07:57:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/qa-correction-erreurs/ig/StructureDefinition-PersonneStructureAuteur.xlsx
+++ b/qa-correction-erreurs/ig/StructureDefinition-PersonneStructureAuteur.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-25T07:57:03+00:00</t>
+    <t>2025-08-25T14:26:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
